--- a/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_25_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste04/content/results/metrics_25_8.xlsx
@@ -513,1211 +513,1211 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_8</t>
+          <t>model_25_8_24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9911416143357695</v>
+        <v>0.9995024140911158</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8578423698754727</v>
+        <v>0.6501498279154057</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8723904796438493</v>
+        <v>0.9974295929401811</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9899487217561499</v>
+        <v>0.9495870059839819</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9848862480703839</v>
+        <v>0.9985917233422967</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05923606572582471</v>
+        <v>0.0002953884901056782</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9506087272184128</v>
+        <v>0.2076861748899413</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1247510716886064</v>
+        <v>0.001452622254469426</v>
       </c>
       <c r="J2" t="n">
-        <v>0.145931476893976</v>
+        <v>0.0003899995227171763</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1353411948154358</v>
+        <v>0.0009213108885933011</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5119630460150986</v>
+        <v>0.007993796430742647</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2433846045373961</v>
+        <v>0.01718686970060803</v>
       </c>
       <c r="N2" t="n">
-        <v>1.003037160799165</v>
+        <v>1.000351237112153</v>
       </c>
       <c r="O2" t="n">
-        <v>0.25374599102814</v>
+        <v>0.01791855032548787</v>
       </c>
       <c r="P2" t="n">
-        <v>193.6524494084974</v>
+        <v>132.2544383047696</v>
       </c>
       <c r="Q2" t="n">
-        <v>308.2267769461082</v>
+        <v>202.9492361471252</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_9</t>
+          <t>model_25_8_23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9910224007527789</v>
+        <v>0.9995121913369155</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8578014717514281</v>
+        <v>0.6501176641444906</v>
       </c>
       <c r="D3" t="n">
-        <v>0.863217473961354</v>
+        <v>0.9974803107800746</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9889154824940757</v>
+        <v>0.9506791411060964</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9835479037512267</v>
+        <v>0.9986200866330395</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06003324750421101</v>
+        <v>0.0002895842946440176</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9508822131622177</v>
+        <v>0.2077052686937591</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1337186023736461</v>
+        <v>0.001423959921534049</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1609327660674795</v>
+        <v>0.0003815506657373274</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1473258509135856</v>
+        <v>0.0009027552955181352</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5396671964259206</v>
+        <v>0.007936659331295554</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2450168310631149</v>
+        <v>0.01701717645921372</v>
       </c>
       <c r="N3" t="n">
-        <v>1.003078034027619</v>
+        <v>1.000344335526883</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2554477048162335</v>
+        <v>0.01774163289149398</v>
       </c>
       <c r="P3" t="n">
-        <v>193.6257134903209</v>
+        <v>132.2941282602497</v>
       </c>
       <c r="Q3" t="n">
-        <v>308.2000410279317</v>
+        <v>202.9889261026054</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_7</t>
+          <t>model_25_8_22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.991197112073968</v>
+        <v>0.9995229094798254</v>
       </c>
       <c r="C4" t="n">
-        <v>0.85775334512344</v>
+        <v>0.6500820163643922</v>
       </c>
       <c r="D4" t="n">
-        <v>0.882588735999977</v>
+        <v>0.9975360779050308</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9910388764916831</v>
+        <v>0.951878481239179</v>
       </c>
       <c r="F4" t="n">
-        <v>0.986326666945195</v>
+        <v>0.9986512646572866</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05886495209494805</v>
+        <v>0.0002832215420130017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9512040361451766</v>
+        <v>0.2077264307559294</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1147812559081591</v>
+        <v>0.001392444070194601</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1301038491296501</v>
+        <v>0.0003722724610084216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1224424776431881</v>
+        <v>0.0008823582712072023</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4817019910046589</v>
+        <v>0.007873984911326886</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2426210050571633</v>
+        <v>0.01682918720595269</v>
       </c>
       <c r="N4" t="n">
-        <v>1.003018133003211</v>
+        <v>1.000336769778947</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2529498835371649</v>
+        <v>0.01754564054653022</v>
       </c>
       <c r="P4" t="n">
-        <v>193.6650188125289</v>
+        <v>132.338562265215</v>
       </c>
       <c r="Q4" t="n">
-        <v>308.2393463501397</v>
+        <v>203.0333601075707</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_10</t>
+          <t>model_25_8_21</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9908600004124986</v>
+        <v>0.9995346633907568</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8576686991125719</v>
+        <v>0.6500424098051873</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8549898602332564</v>
+        <v>0.9975974863344036</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9879442504485408</v>
+        <v>0.9531938901916346</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9823114960700334</v>
+        <v>0.9986855655590092</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06111921932745013</v>
+        <v>0.0002762439127415911</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9517700644096106</v>
+        <v>0.2077499429203876</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1417619178500731</v>
+        <v>0.001357740130685057</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1750337911682789</v>
+        <v>0.0003620963372996693</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1583976809681583</v>
+        <v>0.0008599182243081566</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5651702894856931</v>
+        <v>0.007804068504510764</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2472230153676031</v>
+        <v>0.01662058701555367</v>
       </c>
       <c r="N5" t="n">
-        <v>1.003133714144286</v>
+        <v>1.000328472900642</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2577478109539948</v>
+        <v>0.01732815981416399</v>
       </c>
       <c r="P5" t="n">
-        <v>193.5898578139786</v>
+        <v>132.3884526813993</v>
       </c>
       <c r="Q5" t="n">
-        <v>308.1641853515894</v>
+        <v>203.0832505237549</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_6</t>
+          <t>model_25_8_20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9911614578897869</v>
+        <v>0.9995474777256947</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8574847584065712</v>
+        <v>0.6499983771878661</v>
       </c>
       <c r="D6" t="n">
-        <v>0.893872575177318</v>
+        <v>0.997664700374719</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9921764459314407</v>
+        <v>0.9546325360601571</v>
       </c>
       <c r="F6" t="n">
-        <v>0.987864779863142</v>
+        <v>0.9987231026197111</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05910337178873919</v>
+        <v>0.0002686367699720362</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9530000767576063</v>
+        <v>0.2077760825841396</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1037501743226594</v>
+        <v>0.001319755247939743</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1135878215771497</v>
+        <v>0.000350966841560841</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1086689261752637</v>
+        <v>0.0008353610447502918</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4485358047097978</v>
+        <v>0.00772649759532911</v>
       </c>
       <c r="M6" t="n">
-        <v>0.243111850366738</v>
+        <v>0.0163901424634454</v>
       </c>
       <c r="N6" t="n">
-        <v>1.00303035729493</v>
+        <v>1.000319427487745</v>
       </c>
       <c r="O6" t="n">
-        <v>0.253461625147758</v>
+        <v>0.01708790476038649</v>
       </c>
       <c r="P6" t="n">
-        <v>193.6569346078691</v>
+        <v>132.4443007766747</v>
       </c>
       <c r="Q6" t="n">
-        <v>308.2312621454799</v>
+        <v>203.1390986190303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_11</t>
+          <t>model_25_8_19</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9906699595778758</v>
+        <v>0.9995614749137826</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8574730708986112</v>
+        <v>0.6499495184666302</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8476241094727959</v>
+        <v>0.997738479571187</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9870373720451006</v>
+        <v>0.9562059158274927</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9811742450498189</v>
+        <v>0.9987642719012128</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06239002326362983</v>
+        <v>0.0002603274344760406</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9530782311771503</v>
+        <v>0.2078050872316521</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1489626760583484</v>
+        <v>0.001278060177776877</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1882004851515307</v>
+        <v>0.0003387950320841262</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1685815792217289</v>
+        <v>0.0008084276243065111</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5882810917955863</v>
+        <v>0.007639907815026108</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2497799496829756</v>
+        <v>0.01613466561401384</v>
       </c>
       <c r="N7" t="n">
-        <v>1.003198871001871</v>
+        <v>1.000309547119683</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2604135992567564</v>
+        <v>0.01682155173256464</v>
       </c>
       <c r="P7" t="n">
-        <v>193.5486997999704</v>
+        <v>132.5071407118245</v>
       </c>
       <c r="Q7" t="n">
-        <v>308.1230273375812</v>
+        <v>203.2019385541801</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_12</t>
+          <t>model_25_8_18</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9904637238002354</v>
+        <v>0.9995767078067803</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8572363637776801</v>
+        <v>0.6498953748752436</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8410344179764443</v>
+        <v>0.997819201808454</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9861949793970926</v>
+        <v>0.9579235344899389</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9801316815256396</v>
+        <v>0.9988092929301248</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06376912285834058</v>
+        <v>0.0002512845311658508</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9546610927847533</v>
+        <v>0.2078372292063805</v>
       </c>
       <c r="I8" t="n">
-        <v>0.155404758702126</v>
+        <v>0.001232441365053527</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2004309299035364</v>
+        <v>0.0003255073773506798</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1779175663207975</v>
+        <v>0.0007789743461275413</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6091946547144462</v>
+        <v>0.007543514718700086</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2525254895220294</v>
+        <v>0.01585195669833383</v>
       </c>
       <c r="N8" t="n">
-        <v>1.003269580411348</v>
+        <v>1.000298794489332</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2632760224108097</v>
+        <v>0.016526807313056</v>
       </c>
       <c r="P8" t="n">
-        <v>193.5049723470384</v>
+        <v>132.5778493411173</v>
       </c>
       <c r="Q8" t="n">
-        <v>308.0792998846492</v>
+        <v>203.2726471834729</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_13</t>
+          <t>model_25_8_17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9902500057378809</v>
+        <v>0.9995932029089013</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8569749835558128</v>
+        <v>0.6498350358963481</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8351430800280554</v>
+        <v>0.9979071901661691</v>
       </c>
       <c r="E9" t="n">
-        <v>0.985416092449515</v>
+        <v>0.9597882336023674</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9791786568708835</v>
+        <v>0.9988583186706441</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06519825652538619</v>
+        <v>0.0002414923259955065</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9564089435319247</v>
+        <v>0.2078730490307611</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1611641308923049</v>
+        <v>0.001182716226747901</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2117393545472356</v>
+        <v>0.0003110818948326767</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1864517473807969</v>
+        <v>0.0007469011392652869</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6281056235847654</v>
+        <v>0.00743635159847224</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2553394926864745</v>
+        <v>0.01554002335891123</v>
       </c>
       <c r="N9" t="n">
-        <v>1.003342855175584</v>
+        <v>1.000287150887834</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2662098235157548</v>
+        <v>0.01620159432558314</v>
       </c>
       <c r="P9" t="n">
-        <v>193.4606451016305</v>
+        <v>132.6573457235853</v>
       </c>
       <c r="Q9" t="n">
-        <v>308.0349726392413</v>
+        <v>203.3521435659409</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_5</t>
+          <t>model_25_8_16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9909984246531137</v>
+        <v>0.9996110441702681</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8569715940728044</v>
+        <v>0.6497681502934755</v>
       </c>
       <c r="D10" t="n">
-        <v>0.906271442322286</v>
+        <v>0.9980030786632669</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9933467598337941</v>
+        <v>0.9618106845244707</v>
       </c>
       <c r="F10" t="n">
-        <v>0.989490284817738</v>
+        <v>0.9989116957383012</v>
       </c>
       <c r="G10" t="n">
-        <v>0.06019357579307206</v>
+        <v>0.0002309009825457897</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9564316090204092</v>
+        <v>0.2079127552139339</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09162904135591476</v>
+        <v>0.001128526457738458</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09659638704946007</v>
+        <v>0.0002954360299176004</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09411279320722589</v>
+        <v>0.0007119812438280293</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4123010325943218</v>
+        <v>0.00731682889556878</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2453437910220514</v>
+        <v>0.01519542636933198</v>
       </c>
       <c r="N10" t="n">
-        <v>1.003086254404647</v>
+        <v>1.000274557056281</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2557885841375223</v>
+        <v>0.0158423271287434</v>
       </c>
       <c r="P10" t="n">
-        <v>193.6203792935251</v>
+        <v>132.7470431726516</v>
       </c>
       <c r="Q10" t="n">
-        <v>308.1947068311359</v>
+        <v>203.4418410150072</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_14</t>
+          <t>model_25_8_15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9900350527052735</v>
+        <v>0.9996302717704519</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8567011027517235</v>
+        <v>0.6496938785126067</v>
       </c>
       <c r="D11" t="n">
-        <v>0.829877438307799</v>
+        <v>0.9981072994176471</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9846983830296071</v>
+        <v>0.9639993086824121</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9783094110361022</v>
+        <v>0.9989696509243048</v>
       </c>
       <c r="G11" t="n">
-        <v>0.06663564844419938</v>
+        <v>0.0002194866484876144</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9582403857299755</v>
+        <v>0.2079568461514314</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1663118224273633</v>
+        <v>0.001069627853872607</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2221595611206579</v>
+        <v>0.0002785046336840573</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1942357027093938</v>
+        <v>0.000674066290382339</v>
       </c>
       <c r="L11" t="n">
-        <v>0.645181669412247</v>
+        <v>0.007183329859468643</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2581388162291742</v>
+        <v>0.01481508179145881</v>
       </c>
       <c r="N11" t="n">
-        <v>1.003416553358192</v>
+        <v>1.000260984632622</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2691283200570658</v>
+        <v>0.01544579049476836</v>
       </c>
       <c r="P11" t="n">
-        <v>193.4170311654249</v>
+        <v>132.8484383084696</v>
       </c>
       <c r="Q11" t="n">
-        <v>307.9913587030357</v>
+        <v>203.5432361508252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_15</t>
+          <t>model_25_8_14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9898234525280638</v>
+        <v>0.9996508542479656</v>
       </c>
       <c r="C12" t="n">
-        <v>0.856423774100911</v>
+        <v>0.6496111890465726</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8251700612836159</v>
+        <v>0.998219999604071</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9840391229253187</v>
+        <v>0.9663544144897545</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9775180226702876</v>
+        <v>0.9990322530954522</v>
       </c>
       <c r="G12" t="n">
-        <v>0.06805061980352986</v>
+        <v>0.00020726800071876</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9600948836949397</v>
+        <v>0.2080059341904683</v>
       </c>
       <c r="I12" t="n">
-        <v>0.170913754375467</v>
+        <v>0.001005937241812946</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2317311597116084</v>
+        <v>0.0002602853202165786</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2013224570435377</v>
+        <v>0.0006331112254721276</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6605893783999846</v>
+        <v>0.007034720863717739</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2608651371945471</v>
+        <v>0.01439680522611736</v>
       </c>
       <c r="N12" t="n">
-        <v>1.003489101990378</v>
+        <v>1.000246455824966</v>
       </c>
       <c r="O12" t="n">
-        <v>0.271970706150197</v>
+        <v>0.01500970703008846</v>
       </c>
       <c r="P12" t="n">
-        <v>193.3750068837309</v>
+        <v>132.962995825248</v>
       </c>
       <c r="Q12" t="n">
-        <v>307.9493344213417</v>
+        <v>203.6577936676036</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_16</t>
+          <t>model_25_8_13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9896183855943973</v>
+        <v>0.9996727599835701</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8561494447262882</v>
+        <v>0.6495194394740609</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8209588861955726</v>
+        <v>0.9983414200240531</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9834352277401953</v>
+        <v>0.9688749450159295</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9767985891366474</v>
+        <v>0.999099599641268</v>
       </c>
       <c r="G13" t="n">
-        <v>0.06942190333320407</v>
+        <v>0.0001942638097854652</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9619293254862127</v>
+        <v>0.2080604007000863</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1750305992929587</v>
+        <v>0.0009373185366397132</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2404989317418117</v>
+        <v>0.0002407862660265017</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2077648675374116</v>
+        <v>0.0005890523357433984</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6744905566381284</v>
+        <v>0.006868935765322703</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2634803661246964</v>
+        <v>0.01393785527925531</v>
       </c>
       <c r="N13" t="n">
-        <v>1.003559410653349</v>
+        <v>1.000230992952774</v>
       </c>
       <c r="O13" t="n">
-        <v>0.274697270790173</v>
+        <v>0.01453121863383114</v>
       </c>
       <c r="P13" t="n">
-        <v>193.3351057025504</v>
+        <v>133.0925869567936</v>
       </c>
       <c r="Q13" t="n">
-        <v>307.9094332401612</v>
+        <v>203.7873847991493</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_4</t>
+          <t>model_25_8_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9906599055628856</v>
+        <v>0.9996959084198308</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8561296163979987</v>
+        <v>0.6494173928337243</v>
       </c>
       <c r="D14" t="n">
-        <v>0.919751604130383</v>
+        <v>0.9984716066927976</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9945268257265735</v>
+        <v>0.9715578638459055</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9911827521665292</v>
+        <v>0.9991716925088743</v>
       </c>
       <c r="G14" t="n">
-        <v>0.06245725450816446</v>
+        <v>0.0001805218980607113</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9620619176087857</v>
+        <v>0.2081209799939754</v>
       </c>
       <c r="I14" t="n">
-        <v>0.07845083468761523</v>
+        <v>0.000863745733635235</v>
       </c>
       <c r="J14" t="n">
-        <v>0.07946336631442341</v>
+        <v>0.0002200309610976359</v>
       </c>
       <c r="K14" t="n">
-        <v>0.07895702287049998</v>
+        <v>0.0005418883473664354</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3728819813603972</v>
+        <v>0.006683861875008263</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2499144943939116</v>
+        <v>0.01343584377926118</v>
       </c>
       <c r="N14" t="n">
-        <v>1.003202318092725</v>
+        <v>1.000214652880119</v>
       </c>
       <c r="O14" t="n">
-        <v>0.2605538718145828</v>
+        <v>0.01400783546497519</v>
       </c>
       <c r="P14" t="n">
-        <v>193.546545768189</v>
+        <v>133.2393169373079</v>
       </c>
       <c r="Q14" t="n">
-        <v>308.1208733057998</v>
+        <v>203.9341147796636</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_17</t>
+          <t>model_25_8_11</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9894220513688627</v>
+        <v>0.9997201834464542</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8558827809507344</v>
+        <v>0.6493037410624757</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8171927672329965</v>
+        <v>0.9986105552036607</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9828830652458098</v>
+        <v>0.9743972394083124</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9761454095286826</v>
+        <v>0.9992484949402349</v>
       </c>
       <c r="G15" t="n">
-        <v>0.07073479120338975</v>
+        <v>0.0001661111936305166</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9637125073812143</v>
+        <v>0.2081884485948896</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1787123573261907</v>
+        <v>0.0007852213231399441</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2485156124401541</v>
+        <v>0.0001980652926074519</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2136139848831724</v>
+        <v>0.0004916433078736979</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6870178155937662</v>
+        <v>0.006476951734862042</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2659601308530843</v>
+        <v>0.01288841315408986</v>
       </c>
       <c r="N15" t="n">
-        <v>1.003626725244961</v>
+        <v>1.000197517567209</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2772826042368691</v>
+        <v>0.01343709958475271</v>
       </c>
       <c r="P15" t="n">
-        <v>193.2976354617805</v>
+        <v>133.405706305407</v>
       </c>
       <c r="Q15" t="n">
-        <v>307.8719629993914</v>
+        <v>204.1005041477626</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_18</t>
+          <t>model_25_8_10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9892358469064202</v>
+        <v>0.9997452970589978</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8556268552175801</v>
+        <v>0.6491771325452951</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8138234886599274</v>
+        <v>0.9987575114404594</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9823791621497019</v>
+        <v>0.9773691897388772</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9755530369177328</v>
+        <v>0.9993295373772464</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07197994130113604</v>
+        <v>0.000151202668373005</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9654238839372472</v>
+        <v>0.2082636088798911</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1820061641803717</v>
+        <v>0.0007021714812125604</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2558316294921609</v>
+        <v>0.000175074013611184</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2189185854426658</v>
+        <v>0.0004386244076111868</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6983047950051278</v>
+        <v>0.006245832127057182</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2682907775178566</v>
+        <v>0.01229644942139824</v>
       </c>
       <c r="N16" t="n">
-        <v>1.003690566774942</v>
+        <v>1.000179790311296</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2797124713552644</v>
+        <v>0.01281993473042655</v>
       </c>
       <c r="P16" t="n">
-        <v>193.2627355836402</v>
+        <v>133.5937788928099</v>
       </c>
       <c r="Q16" t="n">
-        <v>307.837063121251</v>
+        <v>204.2885767351655</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_19</t>
+          <t>model_25_8_9</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9890605527569163</v>
+        <v>0.9997708618750102</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8553837658644738</v>
+        <v>0.6490359184132584</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8108052836937117</v>
+        <v>0.9989113062723978</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9819200886809908</v>
+        <v>0.9804459560237347</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9750161226386289</v>
+        <v>0.999414158338109</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07315213408602333</v>
+        <v>0.0001360262892455301</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9670494235607923</v>
+        <v>0.208347439688801</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1849567614638691</v>
+        <v>0.000615256922429902</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2624967787066739</v>
+        <v>0.0001512718688263399</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2237265656441259</v>
+        <v>0.0003832643956281209</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7085156869250941</v>
+        <v>0.00598792995988671</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2704665119493046</v>
+        <v>0.01166303087732902</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0037506676262</v>
+        <v>1.000161744558816</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2819808313058503</v>
+        <v>0.01215955024757915</v>
       </c>
       <c r="P17" t="n">
-        <v>193.2304279556665</v>
+        <v>133.8053247752659</v>
       </c>
       <c r="Q17" t="n">
-        <v>307.8047554932773</v>
+        <v>204.5001226176215</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_20</t>
+          <t>model_25_8_8</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9888966278052842</v>
+        <v>0.9997963425391926</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8551547188622911</v>
+        <v>0.6488782019718188</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8081023946395867</v>
+        <v>0.9990702902117414</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9815025188689679</v>
+        <v>0.9835850392367751</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9745300539533653</v>
+        <v>0.9995013864874008</v>
       </c>
       <c r="G18" t="n">
-        <v>0.07424830099239273</v>
+        <v>0.0001208998662795021</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9685810619190527</v>
+        <v>0.2084410669814351</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1875991059003691</v>
+        <v>0.0005254098270013101</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2685593488491453</v>
+        <v>0.000126987634597636</v>
       </c>
       <c r="K18" t="n">
-        <v>0.2280792318075178</v>
+        <v>0.0003261987307994731</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7177090418782379</v>
+        <v>0.005700146197556176</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2724854142745859</v>
+        <v>0.01099544752520343</v>
       </c>
       <c r="N18" t="n">
-        <v>1.00380687046676</v>
+        <v>1.000143758207629</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2840856824828228</v>
+        <v>0.01146354649006552</v>
       </c>
       <c r="P18" t="n">
-        <v>193.2006807676369</v>
+        <v>134.0410958127726</v>
       </c>
       <c r="Q18" t="n">
-        <v>307.7750083052478</v>
+        <v>204.7358936551282</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_21</t>
+          <t>model_25_8_7</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9887440520870445</v>
+        <v>0.9998210781355369</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8549402995394139</v>
+        <v>0.6487018475457813</v>
       </c>
       <c r="D19" t="n">
-        <v>0.805680421825262</v>
+        <v>0.9992323841554769</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9811230115314966</v>
+        <v>0.9867318105249741</v>
       </c>
       <c r="F19" t="n">
-        <v>0.974090199753529</v>
+        <v>0.9995900033634607</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07526857552280763</v>
+        <v>0.0001062157477674097</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9700148849184431</v>
+        <v>0.2085457585868454</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1899668266107394</v>
+        <v>0.0004338051649750207</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2740693014049988</v>
+        <v>0.0001026439247178418</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2320180547568216</v>
+        <v>0.0002682245448464313</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7259920679251189</v>
+        <v>0.005377971614989358</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2743511901246423</v>
+        <v>0.01030610245279027</v>
       </c>
       <c r="N19" t="n">
-        <v>1.003859182141585</v>
+        <v>1.00012629778668</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2860308882735045</v>
+        <v>0.01074485457077872</v>
       </c>
       <c r="P19" t="n">
-        <v>193.1733851100287</v>
+        <v>134.3000763521744</v>
       </c>
       <c r="Q19" t="n">
-        <v>307.7477126476396</v>
+        <v>204.99487419453</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_3</t>
+          <t>model_25_8_6</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9900820476778408</v>
+        <v>0.9998440357879135</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8548498189270674</v>
+        <v>0.6485043977844305</v>
       </c>
       <c r="D20" t="n">
-        <v>0.934172153348909</v>
+        <v>0.9993938241558097</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9956836971246624</v>
+        <v>0.9898032909645412</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9929077080826415</v>
+        <v>0.9996778926293606</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06632139284624976</v>
+        <v>9.258709359768672e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9706199291898292</v>
+        <v>0.2086629732945689</v>
       </c>
       <c r="I20" t="n">
-        <v>0.06435330525306705</v>
+        <v>0.0003425700680478083</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0626670994512685</v>
+        <v>7.888267171458397e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06351032268792463</v>
+        <v>0.0002107263698811961</v>
       </c>
       <c r="L20" t="n">
-        <v>0.330215986170961</v>
+        <v>0.005017824166548069</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2575294019063644</v>
+        <v>0.009622218746094204</v>
       </c>
       <c r="N20" t="n">
-        <v>1.003400440796169</v>
+        <v>1.000110092385002</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2684929617048724</v>
+        <v>0.01003185651885417</v>
       </c>
       <c r="P20" t="n">
-        <v>193.426485532944</v>
+        <v>134.5747216080418</v>
       </c>
       <c r="Q20" t="n">
-        <v>308.0008130705548</v>
+        <v>205.2695194503974</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_22</t>
+          <t>model_25_8_5</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9886027140941459</v>
+        <v>0.9998639480347431</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8547406330344726</v>
+        <v>0.6482822040406315</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8035095074093814</v>
+        <v>0.9995500724317915</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9807786052067468</v>
+        <v>0.9926951586076554</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9736925377415943</v>
+        <v>0.9997624775234581</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07621370333212253</v>
+        <v>8.076632371536675e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9713500557563655</v>
+        <v>0.2087948770991579</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1920891126217634</v>
+        <v>0.0002542689866892003</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2790696329452304</v>
+        <v>5.65109196972879e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2355790535133567</v>
+        <v>0.0001553899531932441</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7334523435476732</v>
+        <v>0.004613983959231616</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2760682946883298</v>
+        <v>0.00898700860772742</v>
       </c>
       <c r="N21" t="n">
-        <v>1.003907640882007</v>
+        <v>1.000096036681358</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2878210935333647</v>
+        <v>0.009369604169830853</v>
       </c>
       <c r="P21" t="n">
-        <v>193.1484279974056</v>
+        <v>134.8479009300349</v>
       </c>
       <c r="Q21" t="n">
-        <v>307.7227555350164</v>
+        <v>205.5426987723905</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_23</t>
+          <t>model_25_8_4</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9884722110615612</v>
+        <v>0.9998790233582427</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8545556375415214</v>
+        <v>0.6480311788485293</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8015620084408415</v>
+        <v>0.9996942449684169</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9804662749991322</v>
+        <v>0.99526304406065</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9733330259520174</v>
+        <v>0.9998399311187059</v>
       </c>
       <c r="G22" t="n">
-        <v>0.07708637771192722</v>
+        <v>7.181696046594666e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9725871214695554</v>
+        <v>0.2089438964969134</v>
       </c>
       <c r="I22" t="n">
-        <v>0.193992987683434</v>
+        <v>0.0001727923060267719</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2836042610164096</v>
+        <v>3.664552347142431e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2387984232223579</v>
+        <v>0.0001047189147490981</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7401730639432383</v>
+        <v>0.004161641608210483</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2776443367186286</v>
+        <v>0.00847448880263268</v>
       </c>
       <c r="N22" t="n">
-        <v>1.003952384778893</v>
+        <v>1.000085395276535</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2894642309357501</v>
+        <v>0.00883526533557097</v>
       </c>
       <c r="P22" t="n">
-        <v>193.1256573947928</v>
+        <v>135.0827797832331</v>
       </c>
       <c r="Q22" t="n">
-        <v>307.6999849324036</v>
+        <v>205.7775776255887</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_25_8_24</t>
+          <t>model_25_8_3</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9883521558375447</v>
+        <v>0.999886929244537</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8543847426066593</v>
+        <v>0.647746774390593</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7998161403256109</v>
+        <v>0.9998171091814869</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9801833338583898</v>
+        <v>0.9973228567032441</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9730083208302707</v>
+        <v>0.9999051772428426</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0778891875477294</v>
+        <v>6.712368484510444e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9737298966858768</v>
+        <v>0.2091127312687773</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1956997484156593</v>
+        <v>0.0001033576655087848</v>
       </c>
       <c r="J23" t="n">
-        <v>0.287712198090768</v>
+        <v>2.071062487676457e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.2417061048717956</v>
+        <v>6.203414519277467e-05</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7462194305354659</v>
+        <v>0.003654164064945549</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2790863442516122</v>
+        <v>0.008192904542657899</v>
       </c>
       <c r="N23" t="n">
-        <v>1.003993546569985</v>
+        <v>1.000079814650915</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2909676277147799</v>
+        <v>0.008541693450689289</v>
       </c>
       <c r="P23" t="n">
-        <v>193.104936269739</v>
+        <v>135.2179471959026</v>
       </c>
       <c r="Q23" t="n">
-        <v>307.6792638073498</v>
+        <v>205.9127450382583</v>
       </c>
     </row>
     <row r="24">
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9891803116393147</v>
+        <v>0.9998846007786535</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8529925883401426</v>
+        <v>0.6474227761775329</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9492187494129596</v>
+        <v>0.9999061665160925</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9967701204707242</v>
+        <v>0.9986346958886273</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9946097743204572</v>
+        <v>0.9999513994697712</v>
       </c>
       <c r="G24" t="n">
-        <v>0.07235130588798609</v>
+        <v>6.850596277810428e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9830392386763556</v>
+        <v>0.2093050706040438</v>
       </c>
       <c r="I24" t="n">
-        <v>0.04964375239982338</v>
+        <v>5.302841291914348e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>0.04689364660511932</v>
+        <v>1.056211721188302e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.04826859585836223</v>
+        <v>3.179502936888964e-05</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2844113035931022</v>
+        <v>0.003084785449394605</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2689819806009058</v>
+        <v>0.008276832895383612</v>
       </c>
       <c r="N24" t="n">
-        <v>1.003709607437949</v>
+        <v>1.000081458273892</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2804331003845467</v>
+        <v>0.008629194807146178</v>
       </c>
       <c r="P24" t="n">
-        <v>193.252443552951</v>
+        <v>135.177179537258</v>
       </c>
       <c r="Q24" t="n">
-        <v>307.8267710905617</v>
+        <v>205.8719773796136</v>
       </c>
     </row>
     <row r="25">
@@ -1782,52 +1782,52 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9878426423686022</v>
+        <v>0.9998680775051619</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8503803725777935</v>
+        <v>0.6470615813917169</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9643068869142229</v>
+        <v>0.9999435340791037</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9977211552310083</v>
+        <v>0.9989130572160533</v>
       </c>
       <c r="F25" t="n">
-        <v>0.996204317091621</v>
+        <v>0.999969184699349</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08129630646064175</v>
+        <v>7.83148916909146e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.000507137507331</v>
+        <v>0.2095194914317065</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03489358863606673</v>
+        <v>3.191076409460216e-05</v>
       </c>
       <c r="J25" t="n">
-        <v>0.03308585979644273</v>
+        <v>8.408688577897166e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03398972421625472</v>
+        <v>2.015972633624966e-05</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2357513618562808</v>
+        <v>0.002523618893617848</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2851250716100598</v>
+        <v>0.008849570141589625</v>
       </c>
       <c r="N25" t="n">
-        <v>1.004168236902194</v>
+        <v>1.000093121761062</v>
       </c>
       <c r="O25" t="n">
-        <v>0.2972634361987656</v>
+        <v>0.009226314663652722</v>
       </c>
       <c r="P25" t="n">
-        <v>193.0193093888976</v>
+        <v>134.9095455708549</v>
       </c>
       <c r="Q25" t="n">
-        <v>307.5936369265085</v>
+        <v>205.6043434132106</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9859218180783172</v>
+        <v>0.9998679838002852</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8467911166431166</v>
+        <v>0.6470604739748975</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9784415574029979</v>
+        <v>0.9999435406992208</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9984506897041907</v>
+        <v>0.9989147635407157</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9975672787175555</v>
+        <v>0.999969197647394</v>
       </c>
       <c r="G26" t="n">
-        <v>0.09414086733435953</v>
+        <v>7.837051895361157e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.02450850846952</v>
+        <v>0.2095201488421684</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0210755342580025</v>
+        <v>3.190702284697299e-05</v>
       </c>
       <c r="J26" t="n">
-        <v>0.02249396884150764</v>
+        <v>8.395488294578381e-06</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02178462413253009</v>
+        <v>2.015125557538838e-05</v>
       </c>
       <c r="L26" t="n">
-        <v>0.1845222306560777</v>
+        <v>0.002521487459815185</v>
       </c>
       <c r="M26" t="n">
-        <v>0.3068238376240665</v>
+        <v>0.008852712519539509</v>
       </c>
       <c r="N26" t="n">
-        <v>1.004826805230291</v>
+        <v>1.000093187905681</v>
       </c>
       <c r="O26" t="n">
-        <v>0.3198859636046264</v>
+        <v>0.009229590819137554</v>
       </c>
       <c r="P26" t="n">
-        <v>192.7259260596243</v>
+        <v>134.9081254701626</v>
       </c>
       <c r="Q26" t="n">
-        <v>307.3002535972352</v>
+        <v>205.6029233125182</v>
       </c>
     </row>
   </sheetData>
